--- a/Datas/__beans__.xlsx
+++ b/Datas/__beans__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -180,6 +180,60 @@
   </si>
   <si>
     <t>背景故事</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Bean.LuckyBuffParam</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Bean.LuckyBuffParamMoreMeat</t>
+  </si>
+  <si>
+    <t>ExtraMeatDropProbability</t>
+  </si>
+  <si>
+    <t>额外掉落肉概率</t>
+  </si>
+  <si>
+    <t>ExtraMeatDropMultiplier</t>
+  </si>
+  <si>
+    <t>额外掉肉倍率</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Bean.LuckyBuffParamDamageBoost</t>
+  </si>
+  <si>
+    <t>DamageIncreaseMultiplier</t>
+  </si>
+  <si>
+    <t>伤害提升倍率</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Bean.LuckyBuffParamStartSpecialBullet</t>
+  </si>
+  <si>
+    <t>SpecialBulletCount</t>
+  </si>
+  <si>
+    <t>特殊子弹数量</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Bean.LuckyBuffParamStartEnergy</t>
+  </si>
+  <si>
+    <t>EnergyBarCount</t>
+  </si>
+  <si>
+    <t>丰收能量条条数</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Bean.LuckyBuffHighTierSpawn</t>
+  </si>
+  <si>
+    <t>HighTierSpawnWeightMultiplier</t>
+  </si>
+  <si>
+    <t>派发提升倍率</t>
   </si>
 </sst>
 </file>
@@ -799,16 +853,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="23" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1130,260 +1184,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="39.375" customWidth="1"/>
-    <col min="3" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="6" width="12.25" customWidth="1"/>
-    <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="3" width="48.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12.25" style="1" customWidth="1"/>
+    <col min="7" max="9" width="15" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="13.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="28.625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="B5" s="4"/>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="B7" s="4"/>
-      <c r="J7" t="s">
+      <c r="J7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="B9" s="4"/>
-      <c r="J9" t="s">
+      <c r="J9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:16">
-      <c r="B10" s="4"/>
-      <c r="J10" t="s">
+      <c r="J10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N10" t="s">
+      <c r="N10" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="B11" s="4"/>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N11" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="B12" s="4"/>
-      <c r="J12" t="s">
+      <c r="J12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N12" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="B13" s="4"/>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N13" t="s">
+      <c r="N13" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="B14" s="4"/>
-      <c r="J14" t="s">
+      <c r="J14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N14" t="s">
+      <c r="N14" s="1" t="s">
         <v>50</v>
       </c>
     </row>
+    <row r="15" spans="1:16">
+      <c r="B15" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="B16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16"/>
+      <c r="J16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="J17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18"/>
+      <c r="J18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19"/>
+      <c r="J19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20"/>
+      <c r="J20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B14"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Datas/__beans__.xlsx
+++ b/Datas/__beans__.xlsx
@@ -122,16 +122,16 @@
     <t>HuntingConfig.Bean.MeatProgressReward</t>
   </si>
   <si>
-    <t>Coin</t>
-  </si>
-  <si>
-    <t>3币奖励</t>
-  </si>
-  <si>
-    <t>Mastery</t>
-  </si>
-  <si>
-    <t>熟练度奖励</t>
+    <t>ThreeKPCoin</t>
+  </si>
+  <si>
+    <t>3币</t>
+  </si>
+  <si>
+    <t>Point</t>
+  </si>
+  <si>
+    <t>积分</t>
   </si>
   <si>
     <t>HuntingConfig.Bean.RoleProfile</t>

--- a/Datas/__beans__.xlsx
+++ b/Datas/__beans__.xlsx
@@ -95,7 +95,7 @@
     <t>字段变体</t>
   </si>
   <si>
-    <t>HuntingConfig.Bean.SpecieWeight</t>
+    <t>HuntingConfig.Bean.MapSpecies</t>
   </si>
   <si>
     <t>,</t>

--- a/Datas/__beans__.xlsx
+++ b/Datas/__beans__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="78">
   <si>
     <t>##var</t>
   </si>
@@ -234,6 +234,33 @@
   </si>
   <si>
     <t>派发提升倍率</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Bean.QuestGlobal</t>
+  </si>
+  <si>
+    <t>StartDispatchTime</t>
+  </si>
+  <si>
+    <t>任务起始派发时间</t>
+  </si>
+  <si>
+    <t>DispatchInterval</t>
+  </si>
+  <si>
+    <t>任务派发间隔</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>任务持续时间</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
 </sst>
 </file>
@@ -1184,16 +1211,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="3" width="48.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.25" style="1" customWidth="1"/>
-    <col min="7" max="9" width="15" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="4.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.25" style="1" customWidth="1"/>
+    <col min="6" max="9" width="4.625" style="1" customWidth="1"/>
     <col min="10" max="10" width="28.625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="13.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="4.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" style="1" customWidth="1"/>
     <col min="13" max="13" width="10.375" style="1" customWidth="1"/>
     <col min="14" max="14" width="28.625" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
@@ -1263,7 +1292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" ht="28" customHeight="1" spans="1:16">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1292,7 +1321,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" ht="28" customHeight="1" spans="2:14">
       <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
@@ -1309,7 +1338,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" ht="28" customHeight="1" spans="10:14">
       <c r="J5" s="1" t="s">
         <v>27</v>
       </c>
@@ -1320,7 +1349,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" ht="28" customHeight="1" spans="2:14">
       <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
@@ -1337,7 +1366,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" ht="28" customHeight="1" spans="10:14">
       <c r="J7" s="1" t="s">
         <v>33</v>
       </c>
@@ -1348,7 +1377,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" ht="28" customHeight="1" spans="2:14">
       <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
@@ -1362,7 +1391,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" ht="28" customHeight="1" spans="10:14">
       <c r="J9" s="1" t="s">
         <v>39</v>
       </c>
@@ -1373,7 +1402,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" ht="28" customHeight="1" spans="10:14">
       <c r="J10" s="1" t="s">
         <v>41</v>
       </c>
@@ -1384,7 +1413,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" ht="28" customHeight="1" spans="10:14">
       <c r="J11" s="1" t="s">
         <v>43</v>
       </c>
@@ -1395,7 +1424,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" ht="28" customHeight="1" spans="10:14">
       <c r="J12" s="1" t="s">
         <v>45</v>
       </c>
@@ -1406,7 +1435,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" ht="28" customHeight="1" spans="10:14">
       <c r="J13" s="1" t="s">
         <v>47</v>
       </c>
@@ -1417,7 +1446,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" ht="28" customHeight="1" spans="10:14">
       <c r="J14" s="1" t="s">
         <v>49</v>
       </c>
@@ -1428,12 +1457,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" ht="28" customHeight="1" spans="2:2">
       <c r="B15" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" ht="28" customHeight="1" spans="2:14">
       <c r="B16" s="1" t="s">
         <v>52</v>
       </c>
@@ -1451,7 +1480,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="2:14">
+    <row r="17" ht="28" customHeight="1" spans="5:14">
       <c r="E17"/>
       <c r="F17"/>
       <c r="J17" s="1" t="s">
@@ -1464,7 +1493,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="2:14">
+    <row r="18" ht="28" customHeight="1" spans="2:14">
       <c r="B18" s="1" t="s">
         <v>57</v>
       </c>
@@ -1482,7 +1511,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="2:14">
+    <row r="19" ht="28" customHeight="1" spans="2:14">
       <c r="B19" s="1" t="s">
         <v>60</v>
       </c>
@@ -1500,7 +1529,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="2:14">
+    <row r="20" ht="28" customHeight="1" spans="2:14">
       <c r="B20" s="1" t="s">
         <v>63</v>
       </c>
@@ -1518,7 +1547,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="2:14">
+    <row r="21" ht="28" customHeight="1" spans="2:14">
       <c r="B21" s="1" t="s">
         <v>66</v>
       </c>
@@ -1535,13 +1564,76 @@
         <v>68</v>
       </c>
     </row>
+    <row r="22" ht="28" customHeight="1" spans="2:14">
+      <c r="B22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="10:14">
+      <c r="J23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="10:14">
+      <c r="J24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="10:14">
+      <c r="J25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1"/>
+    <row r="27" ht="28" customHeight="1"/>
+    <row r="28" ht="28" customHeight="1"/>
+    <row r="29" ht="28" customHeight="1"/>
+    <row r="30" ht="28" customHeight="1"/>
+    <row r="31" ht="28" customHeight="1"/>
+    <row r="32" ht="28" customHeight="1"/>
+    <row r="33" ht="28" customHeight="1"/>
+    <row r="34" ht="28" customHeight="1"/>
+    <row r="35" ht="28" customHeight="1"/>
+    <row r="36" ht="28" customHeight="1"/>
+    <row r="37" ht="28" customHeight="1"/>
+    <row r="38" ht="28" customHeight="1"/>
+    <row r="39" ht="28" customHeight="1"/>
+    <row r="40" ht="28" customHeight="1"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B14"/>
     <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B22:B25"/>
     <mergeCell ref="C16:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/__beans__.xlsx
+++ b/Datas/__beans__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -146,36 +146,6 @@
     <t>角色名称</t>
   </si>
   <si>
-    <t>Birthplace</t>
-  </si>
-  <si>
-    <t>出生地</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>身高</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>性别</t>
-  </si>
-  <si>
-    <t>Traits</t>
-  </si>
-  <si>
-    <t>特征描述</t>
-  </si>
-  <si>
-    <t>Personality</t>
-  </si>
-  <si>
-    <t>个性描述</t>
-  </si>
-  <si>
     <t>BackgroundStory</t>
   </si>
   <si>
@@ -207,15 +177,6 @@
   </si>
   <si>
     <t>伤害提升倍率</t>
-  </si>
-  <si>
-    <t>HuntingConfig.Bean.LuckyBuffParamStartSpecialBullet</t>
-  </si>
-  <si>
-    <t>SpecialBulletCount</t>
-  </si>
-  <si>
-    <t>特殊子弹数量</t>
   </si>
   <si>
     <t>HuntingConfig.Bean.LuckyBuffParamStartEnergy</t>
@@ -1211,7 +1172,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1402,215 +1363,148 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1" spans="10:14">
-      <c r="J10" s="1" t="s">
+    <row r="10" ht="28" customHeight="1" spans="2:2">
+      <c r="B10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N10" s="1" t="s">
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="2:14">
+      <c r="B11" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="10:14">
+      <c r="C11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11"/>
       <c r="J11" s="1" t="s">
         <v>43</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1" spans="10:14">
+    <row r="12" ht="28" customHeight="1" spans="5:14">
+      <c r="E12"/>
+      <c r="F12"/>
       <c r="J12" s="1" t="s">
         <v>45</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1" spans="10:14">
+    <row r="13" ht="28" customHeight="1" spans="2:14">
+      <c r="B13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13"/>
       <c r="J13" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="10:14">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="2:14">
+      <c r="B14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14"/>
       <c r="J14" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="2:2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="2:14">
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="2:14">
       <c r="B16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16"/>
+        <v>56</v>
+      </c>
       <c r="J16" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="5:14">
-      <c r="E17"/>
-      <c r="F17"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="10:14">
       <c r="J17" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="2:14">
-      <c r="B18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="10:14">
       <c r="J18" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="2:14">
-      <c r="B19" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="10:14">
       <c r="J19" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="2:14">
-      <c r="B20" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20"/>
-      <c r="J20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="2:14">
-      <c r="B21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="2:14">
-      <c r="B22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="10:14">
-      <c r="J23" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="10:14">
-      <c r="J24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="10:14">
-      <c r="J25" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
+    </row>
+    <row r="20" ht="28" customHeight="1"/>
+    <row r="21" ht="28" customHeight="1"/>
+    <row r="22" ht="28" customHeight="1"/>
+    <row r="23" ht="28" customHeight="1"/>
+    <row r="24" ht="28" customHeight="1"/>
+    <row r="25" ht="28" customHeight="1"/>
     <row r="26" ht="28" customHeight="1"/>
     <row r="27" ht="28" customHeight="1"/>
     <row r="28" ht="28" customHeight="1"/>
@@ -1620,21 +1514,15 @@
     <row r="32" ht="28" customHeight="1"/>
     <row r="33" ht="28" customHeight="1"/>
     <row r="34" ht="28" customHeight="1"/>
-    <row r="35" ht="28" customHeight="1"/>
-    <row r="36" ht="28" customHeight="1"/>
-    <row r="37" ht="28" customHeight="1"/>
-    <row r="38" ht="28" customHeight="1"/>
-    <row r="39" ht="28" customHeight="1"/>
-    <row r="40" ht="28" customHeight="1"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B14"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="C11:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
